--- a/公的年金等に係る雑所得_excel.xlsx
+++ b/公的年金等に係る雑所得_excel.xlsx
@@ -5,20 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\克彦\30_個人年金\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pukkun\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DDB765-E834-418A-83F1-724D19DEA157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F0B03C2-9AC3-4FA7-B148-2F60D680F71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{67CE2073-415D-4BC5-85F0-AAA223242EC9}"/>
   </bookViews>
   <sheets>
     <sheet name="公的年金等に係る雑所得" sheetId="1" r:id="rId1"/>
+    <sheet name="公的年金等以外の年金に係る雑所得" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">公的年金等に係る雑所得!$A$1:$E$54</definedName>
-    <definedName name="table65歳以上">公的年金等に係る雑所得!$B$18:$C$23</definedName>
-    <definedName name="table65歳未満">公的年金等に係る雑所得!$B$12:$C$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">公的年金等に係る雑所得!$A$1:$E$58</definedName>
+    <definedName name="table65歳以上">公的年金等に係る雑所得!$B$22:$C$27</definedName>
+    <definedName name="table65歳未満">公的年金等に係る雑所得!$B$16:$C$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="84">
   <si>
     <t>判定区分コード</t>
   </si>
@@ -232,16 +233,209 @@
   </si>
   <si>
     <t>330万円以上410万円未満</t>
+  </si>
+  <si>
+    <t>生命保険契約や生命共済契約に基づく年金、互助年金など</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>〈公的年金等以外の年金〉</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>〈公的年金等〉</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>国民年金、厚生年金、恩給、確定給付企業年金、確定拠出年金、一定の外国年金など</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>公的年金等以外の年金に係る雑所得 計算シート</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◇公的年金等以外の年金に係る雑所得の計算方法</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>収入金額－必要経費＝雑所得の金額</t>
+  </si>
+  <si>
+    <t>収入金額＝公的年金等以外の年金の収入金額＋剰余金や割戻金</t>
+  </si>
+  <si>
+    <t>必要経費＝公的年金等以外の年金の収入金額×(保険料又は掛金の総額÷年金の支払総額又は支払総額の見込み額)</t>
+  </si>
+  <si>
+    <t>注：住民税を算出する際の年金等に係る雑所得の計算方法も同様になります。</t>
+  </si>
+  <si>
+    <t>詳しくは、お住まいの市区町村の窓口にお尋ねください。</t>
+  </si>
+  <si>
+    <t>保険料又は掛金の総額</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>年数</t>
+    <rPh sb="0" eb="2">
+      <t>ネンスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>支払開始</t>
+    <rPh sb="0" eb="2">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>支払終了</t>
+    <rPh sb="0" eb="2">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>支払い金額</t>
+    <rPh sb="0" eb="2">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>円</t>
+    <rPh sb="0" eb="1">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>支払い総額</t>
+    <rPh sb="0" eb="2">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ソウガク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>月払</t>
+  </si>
+  <si>
+    <t>公的年金等以外の年金の収入金額</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>年金受取(年)</t>
+    <rPh sb="0" eb="2">
+      <t>ネンキン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ウケト</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>受取期間</t>
+    <rPh sb="0" eb="2">
+      <t>ウケト</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>年</t>
+    <rPh sb="0" eb="1">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>公的年金等以外の年金の収入金額×(保険料又は掛金の総額÷年金の支払総額又は支払総額の見込み額)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>×(</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>÷</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>必要経費=</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケイヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>=</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>雑所得の金額=</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>収入金額－必要経費</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>－</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>下記塗りつぶしの情報を入力してください</t>
+    <rPh sb="0" eb="2">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="6">
+    <numFmt numFmtId="5" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;\-#,##0"/>
+    <numFmt numFmtId="7" formatCode="&quot;¥&quot;#,##0.00;&quot;¥&quot;\-#,##0.00"/>
     <numFmt numFmtId="176" formatCode="#,##0&quot;円&quot;"/>
+    <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="178" formatCode="#&quot;年&quot;"/>
+    <numFmt numFmtId="179" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,8 +487,26 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -323,6 +535,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -557,97 +781,150 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFF2CC"/>
+      <color rgb="FFFFFF99"/>
+      <color rgb="FFFFFFCC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -667,13 +944,13 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>144517</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>52552</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
           <xdr:colOff>277867</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>62077</xdr:rowOff>
         </xdr:to>
         <xdr:pic>
@@ -689,7 +966,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$G$30:$I$44" spid="_x0000_s1028"/>
+                  <a14:cameraTool cellRange="$G$34:$I$48" spid="_x0000_s1035"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1049,470 +1326,766 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="32" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11.125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="27.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="26.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9" style="3"/>
-    <col min="7" max="7" width="15.75" style="26" customWidth="1"/>
-    <col min="8" max="8" width="21.375" style="26" customWidth="1"/>
-    <col min="9" max="9" width="29.625" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="9" style="26"/>
-    <col min="16" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="32" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9" style="2"/>
+    <col min="7" max="7" width="15.75" style="20" customWidth="1"/>
+    <col min="8" max="8" width="21.375" style="20" customWidth="1"/>
+    <col min="9" max="9" width="29.625" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="9" style="20"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A3" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+    </row>
+    <row r="4" spans="1:5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="35"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B6" s="19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B7" s="19">
+        <v>1100001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2">
+        <f>IF(B6="65歳以上",VLOOKUP(B7,table65歳以上,2,TRUE),VLOOKUP(B7,table65歳未満,2,TRUE))</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4">
+        <f>ROUNDDOWN(IF(OR($B$8=1,$B$8=11),0,IF($B$8=2,$B$7-600000,IF($B$8=12,$B$7-1100000,IF($B$8=3,$B$7*0.75-275000,IF($B$8=4,$B$7*0.85-685000,IF($B$8=5,$B$7*0.95-1455000,B7-1955000)))))),0)</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="B14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="10">
+        <v>0</v>
+      </c>
+      <c r="C16" s="11">
+        <v>1</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" s="43"/>
+      <c r="B17" s="13">
+        <v>600001</v>
+      </c>
+      <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" s="43"/>
+      <c r="B18" s="13">
+        <v>1300000</v>
+      </c>
+      <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19" s="43"/>
+      <c r="B19" s="13">
+        <v>4100000</v>
+      </c>
+      <c r="C19" s="14">
+        <v>4</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" s="43"/>
+      <c r="B20" s="13">
+        <v>7700000</v>
+      </c>
+      <c r="C20" s="14">
+        <v>5</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" s="44"/>
+      <c r="B21" s="16">
+        <v>10000000</v>
+      </c>
+      <c r="C21" s="17">
+        <v>6</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A22" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="10">
+        <v>0</v>
+      </c>
+      <c r="C22" s="11">
+        <v>11</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A23" s="43"/>
+      <c r="B23" s="13">
+        <v>1100001</v>
+      </c>
+      <c r="C23" s="14">
+        <v>12</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A24" s="43"/>
+      <c r="B24" s="13">
         <v>3300000</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="3">
-        <f>IF(B2="65歳以上",VLOOKUP(B3,table65歳以上,2,TRUE),VLOOKUP(B3,table65歳未満,2,TRUE))</f>
+      <c r="C24" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5">
-        <f>ROUNDDOWN(IF(OR($B$4=1,$B$4=11),0,IF($B$4=2,$B$3-600000,IF($B$4=12,$B$3-1100000,IF($B$4=3,$B$3*0.75-275000,IF($B$4=4,$B$3*0.85-685000,IF($B$4=5,$B$3*0.95-1455000,B3-1955000)))))),0)</f>
-        <v>2200000</v>
-      </c>
-      <c r="C5" s="6"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B10" s="4" t="s">
+      <c r="D24" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A25" s="43"/>
+      <c r="B25" s="13">
+        <v>4100000</v>
+      </c>
+      <c r="C25" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8" t="s">
+      <c r="D25" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A26" s="43"/>
+      <c r="B26" s="13">
+        <v>7700000</v>
+      </c>
+      <c r="C26" s="14">
         <v>5</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="D26" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A27" s="44"/>
+      <c r="B27" s="16">
+        <v>10000000</v>
+      </c>
+      <c r="C27" s="17">
         <v>6</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A12" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0</v>
-      </c>
-      <c r="C12" s="13">
-        <v>1</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16">
-        <v>600001</v>
-      </c>
-      <c r="C13" s="17">
-        <v>2</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="18" t="s">
+      <c r="D27" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A31" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A32" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="F33" s="20"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A34" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="F35" s="20"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A37" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G38" s="39"/>
+      <c r="H38" s="21" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A14" s="15"/>
-      <c r="B14" s="16">
-        <v>1300000</v>
-      </c>
-      <c r="C14" s="17">
-        <v>3</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="18" t="s">
+      <c r="I38" s="21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G39" s="39"/>
+      <c r="H39" s="21" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16">
-        <v>4100000</v>
-      </c>
-      <c r="C15" s="17">
-        <v>4</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="18" t="s">
+      <c r="I39" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G40" s="39"/>
+      <c r="H40" s="21" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A16" s="15"/>
-      <c r="B16" s="16">
-        <v>7700000</v>
-      </c>
-      <c r="C16" s="17">
-        <v>5</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="18" t="s">
+      <c r="I40" s="21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G41" s="39"/>
+      <c r="H41" s="21" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20">
-        <v>10000000</v>
-      </c>
-      <c r="C17" s="21">
-        <v>6</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="22" t="s">
+      <c r="I41" s="21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G42" s="40"/>
+      <c r="H42" s="21" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="12">
-        <v>0</v>
-      </c>
-      <c r="C18" s="13">
-        <v>11</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="15"/>
-      <c r="B19" s="16">
-        <v>1100001</v>
-      </c>
-      <c r="C19" s="17">
-        <v>12</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="18" t="s">
+      <c r="I42" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G43" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="I43" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G44" s="39"/>
+      <c r="H44" s="21" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" s="15"/>
-      <c r="B20" s="16">
-        <v>3300000</v>
-      </c>
-      <c r="C20" s="17">
-        <v>3</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="18" t="s">
+      <c r="I44" s="21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G45" s="39"/>
+      <c r="H45" s="21" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="15"/>
-      <c r="B21" s="16">
-        <v>4100000</v>
-      </c>
-      <c r="C21" s="17">
-        <v>4</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="18" t="s">
+      <c r="I45" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G46" s="39"/>
+      <c r="H46" s="21" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="15"/>
-      <c r="B22" s="16">
-        <v>7700000</v>
-      </c>
-      <c r="C22" s="17">
-        <v>5</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="18" t="s">
+      <c r="I46" s="21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G47" s="39"/>
+      <c r="H47" s="21" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="19"/>
-      <c r="B23" s="20">
-        <v>10000000</v>
-      </c>
-      <c r="C23" s="21">
-        <v>6</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="22" t="s">
+      <c r="I47" s="21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G48" s="40"/>
+      <c r="H48" s="21" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="F29" s="26"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="F31" s="26"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="28" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="I33" s="27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G34" s="30"/>
-      <c r="H34" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="I34" s="27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G35" s="30"/>
-      <c r="H35" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="I35" s="27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G36" s="30"/>
-      <c r="H36" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="I36" s="27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G37" s="30"/>
-      <c r="H37" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="I37" s="27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G38" s="31"/>
-      <c r="H38" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="I38" s="27" t="s">
+      <c r="I48" s="21" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G39" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="H39" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="I39" s="27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G40" s="30"/>
-      <c r="H40" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="I40" s="27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G41" s="30"/>
-      <c r="H41" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="I41" s="27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G42" s="30"/>
-      <c r="H42" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="I42" s="27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G43" s="30"/>
-      <c r="H43" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="I43" s="27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G44" s="31"/>
-      <c r="H44" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="I44" s="27" t="s">
-        <v>47</v>
-      </c>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="CQoS3uvq7IxPQMLUndP9GXKCp06h1xXbabSUuUt3e5BXRu0JvdpWOSS8CyI8U/lb3QFAw4W6XvfRl20kRylK4A==" saltValue="Ef+V8Sajjp+qdKMrqmhS2g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="9">
-    <mergeCell ref="G39:G44"/>
-    <mergeCell ref="G33:G38"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A18:A23"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="G43:G48"/>
+    <mergeCell ref="G37:G42"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A22:A27"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{A89A5BEC-3332-4E1E-ABA9-E88657416BAC}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{A89A5BEC-3332-4E1E-ABA9-E88657416BAC}">
       <formula1>"65歳未満,65歳以上"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A37" r:id="rId1" xr:uid="{CC578C3A-EFD4-46D9-853A-81E96413C98E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="67" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup paperSize="9" scale="67" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId2"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="5" max="16383" man="1"/>
+  </rowBreaks>
+  <drawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C910452-5802-4207-B795-97CB9519D797}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+    <col min="2" max="2" width="11.125" customWidth="1"/>
+    <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.75" customWidth="1"/>
+    <col min="6" max="6" width="11.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="35"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="32">
+        <v>1000000</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="33">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="27">
+        <f>C14*C15</f>
+        <v>10000000</v>
+      </c>
+      <c r="D16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="31"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="32">
+        <v>8000</v>
+      </c>
+      <c r="D18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="26">
+        <f>IF(A18="月払",C18*12*B19,IF(A18="年払",C18*B19,C18))</f>
+        <v>3168000</v>
+      </c>
+      <c r="G18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="25">
+        <f>DATEDIF(C20,C21,"y")</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="34">
+        <v>34129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="34">
+        <v>46546</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="27">
+        <f>C14</f>
+        <v>1000000</v>
+      </c>
+      <c r="C23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="26">
+        <f>F18</f>
+        <v>3168000</v>
+      </c>
+      <c r="E23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" s="27">
+        <f>C16</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="27">
+        <f>C14*(F18/C16)</f>
+        <v>316800</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="27">
+        <f>C14</f>
+        <v>1000000</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="27">
+        <f>B24</f>
+        <v>316800</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="29">
+        <f>C14-D26</f>
+        <v>683200</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="m7K9v/bn/0aaA+o+Z60WLbuF0EdFWGHolglUCk4THWsJoDB3hMAir1vnGrB5CrtAa8iZNUBHRu6/EQpvB1trFA==" saltValue="I4kotqym/Zk3lrG+MkTWVA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <phoneticPr fontId="2"/>
+  <conditionalFormatting sqref="B19 C20:C21">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$A$18="保険料または掛金の総額"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A18" xr:uid="{99753228-6910-47FC-9D53-6558D246FD5E}">
+      <formula1>"月払,年払,保険料または掛金の総額"</formula1>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C20:C21" xr:uid="{18BC09BF-9D74-48A6-A80C-12956D894A79}">
+      <formula1>1</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18 C15" xr:uid="{47A476B3-12F0-41BC-8808-627E143F33C6}">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{9B838716-2E88-47D5-81EC-CBAEC34BED5D}">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A31" r:id="rId1" xr:uid="{95C1AADB-82A6-4B9C-BDD0-DC45D84AC9BE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/公的年金等に係る雑所得_excel.xlsx
+++ b/公的年金等に係る雑所得_excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pukkun\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F0B03C2-9AC3-4FA7-B148-2F60D680F71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47AB1C4-6E53-4397-9BBF-D7AF9EC8AFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{67CE2073-415D-4BC5-85F0-AAA223242EC9}"/>
   </bookViews>
@@ -789,119 +789,125 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -966,7 +972,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$G$34:$I$48" spid="_x0000_s1035"/>
+                  <a14:cameraTool cellRange="$G$34:$I$48" spid="_x0000_s1039"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1329,462 +1335,463 @@
   <dimension ref="A1:O48"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="32" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="27.875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="26.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9" style="2"/>
-    <col min="7" max="7" width="15.75" style="20" customWidth="1"/>
-    <col min="8" max="8" width="21.375" style="20" customWidth="1"/>
-    <col min="9" max="9" width="29.625" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="9" style="20"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="32" style="4" customWidth="1"/>
+    <col min="2" max="2" width="22" style="4" customWidth="1"/>
+    <col min="3" max="3" width="11.125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="27.875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="26.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="9" style="4"/>
+    <col min="7" max="7" width="15.75" style="17" customWidth="1"/>
+    <col min="8" max="8" width="21.375" style="17" customWidth="1"/>
+    <col min="9" max="9" width="29.625" style="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="9" style="17"/>
+    <col min="16" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.25" x14ac:dyDescent="0.4">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-    </row>
-    <row r="4" spans="1:5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="35" t="s">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+    </row>
+    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="35"/>
+      <c r="B4" s="5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="1">
         <v>1100001</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="4">
         <f>IF(B6="65歳以上",VLOOKUP(B7,table65歳以上,2,TRUE),VLOOKUP(B7,table65歳未満,2,TRUE))</f>
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="21">
         <f>ROUNDDOWN(IF(OR($B$8=1,$B$8=11),0,IF($B$8=2,$B$7-600000,IF($B$8=12,$B$7-1100000,IF($B$8=3,$B$7*0.75-275000,IF($B$8=4,$B$7*0.85-685000,IF($B$8=5,$B$7*0.95-1455000,B7-1955000)))))),0)</f>
         <v>1</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="22"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="20" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="20" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7" t="s">
+      <c r="A15" s="23"/>
+      <c r="B15" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="28">
         <v>0</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="29">
         <v>1</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="30" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A17" s="43"/>
-      <c r="B17" s="13">
+      <c r="A17" s="31"/>
+      <c r="B17" s="32">
         <v>600001</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="33">
         <v>2</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="34" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A18" s="43"/>
-      <c r="B18" s="13">
+      <c r="A18" s="31"/>
+      <c r="B18" s="32">
         <v>1300000</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="33">
         <v>3</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="34" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A19" s="43"/>
-      <c r="B19" s="13">
+      <c r="A19" s="31"/>
+      <c r="B19" s="32">
         <v>4100000</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="33">
         <v>4</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="34" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A20" s="43"/>
-      <c r="B20" s="13">
+      <c r="A20" s="31"/>
+      <c r="B20" s="32">
         <v>7700000</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="33">
         <v>5</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="34" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A21" s="44"/>
-      <c r="B21" s="16">
+      <c r="A21" s="35"/>
+      <c r="B21" s="36">
         <v>10000000</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="37">
         <v>6</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="38" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="28">
         <v>0</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="29">
         <v>11</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="30" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A23" s="43"/>
-      <c r="B23" s="13">
+      <c r="A23" s="31"/>
+      <c r="B23" s="32">
         <v>1100001</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="33">
         <v>12</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="34" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A24" s="43"/>
-      <c r="B24" s="13">
+      <c r="A24" s="31"/>
+      <c r="B24" s="32">
         <v>3300000</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="33">
         <v>3</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="34" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A25" s="43"/>
-      <c r="B25" s="13">
+      <c r="A25" s="31"/>
+      <c r="B25" s="32">
         <v>4100000</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="33">
         <v>4</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="34" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A26" s="43"/>
-      <c r="B26" s="13">
+      <c r="A26" s="31"/>
+      <c r="B26" s="32">
         <v>7700000</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="33">
         <v>5</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="34" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A27" s="44"/>
-      <c r="B27" s="16">
+      <c r="A27" s="35"/>
+      <c r="B27" s="36">
         <v>10000000</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="37">
         <v>6</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="38" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="20" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A31" s="37" t="s">
+      <c r="A31" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="37"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A32" s="37" t="s">
+      <c r="A32" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="F33" s="20"/>
+      <c r="F33" s="17"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="23" t="s">
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="40" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="F35" s="20"/>
+      <c r="F35" s="17"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
+      <c r="A36" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22" t="s">
+      <c r="G36" s="41"/>
+      <c r="H36" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="22" t="s">
+      <c r="I36" s="41" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G37" s="38" t="s">
+      <c r="G37" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="H37" s="21" t="s">
+      <c r="H37" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="I37" s="21" t="s">
+      <c r="I37" s="43" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G38" s="39"/>
-      <c r="H38" s="21" t="s">
+      <c r="G38" s="44"/>
+      <c r="H38" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="I38" s="43" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G39" s="39"/>
-      <c r="H39" s="21" t="s">
+      <c r="G39" s="44"/>
+      <c r="H39" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="I39" s="21" t="s">
+      <c r="I39" s="43" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G40" s="39"/>
-      <c r="H40" s="21" t="s">
+      <c r="G40" s="44"/>
+      <c r="H40" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="I40" s="21" t="s">
+      <c r="I40" s="43" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G41" s="39"/>
-      <c r="H41" s="21" t="s">
+      <c r="G41" s="44"/>
+      <c r="H41" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="I41" s="21" t="s">
+      <c r="I41" s="43" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G42" s="40"/>
-      <c r="H42" s="21" t="s">
+      <c r="G42" s="45"/>
+      <c r="H42" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="I42" s="21" t="s">
+      <c r="I42" s="43" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G43" s="38" t="s">
+      <c r="G43" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="H43" s="21" t="s">
+      <c r="H43" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="I43" s="21" t="s">
+      <c r="I43" s="43" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G44" s="39"/>
-      <c r="H44" s="21" t="s">
+      <c r="G44" s="44"/>
+      <c r="H44" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="I44" s="21" t="s">
+      <c r="I44" s="43" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G45" s="39"/>
-      <c r="H45" s="21" t="s">
+      <c r="G45" s="44"/>
+      <c r="H45" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="I45" s="21" t="s">
+      <c r="I45" s="43" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G46" s="39"/>
-      <c r="H46" s="21" t="s">
+      <c r="G46" s="44"/>
+      <c r="H46" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="I46" s="21" t="s">
+      <c r="I46" s="43" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G47" s="39"/>
-      <c r="H47" s="21" t="s">
+      <c r="G47" s="44"/>
+      <c r="H47" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="I47" s="21" t="s">
+      <c r="I47" s="43" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G48" s="40"/>
-      <c r="H48" s="21" t="s">
+      <c r="G48" s="45"/>
+      <c r="H48" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="I48" s="21" t="s">
+      <c r="I48" s="43" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="k4TK1c9kAUpXNDuarLCQFKKyVSAk4fdxTv1MB5DUbdviQJU2F1HFL5AzLEuxC7rckFgLcy+qzEK3cAqyaMbSVw==" saltValue="IOEHnAujlSLNSgclMF3GDA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="9">
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A12:D12"/>
@@ -1820,248 +1827,249 @@
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="23.125" customWidth="1"/>
-    <col min="2" max="2" width="11.125" customWidth="1"/>
-    <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.75" customWidth="1"/>
-    <col min="6" max="6" width="11.125" customWidth="1"/>
+    <col min="1" max="1" width="23.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20.25" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="5"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="14">
         <v>1000000</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="15">
         <v>10</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="6">
         <f>C14*C15</f>
         <v>10000000</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="31"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="14">
         <v>8000</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="8">
         <f>IF(A18="月払",C18*12*B19,IF(A18="年払",C18*B19,C18))</f>
         <v>3168000</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="9">
         <f>DATEDIF(C20,C21,"y")</f>
         <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="16">
         <v>34129</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="16">
         <v>46546</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="6">
         <f>C14</f>
         <v>1000000</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="8">
         <f>F18</f>
         <v>3168000</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="6">
         <f>C16</f>
         <v>10000000</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="6">
         <f>C14*(F18/C16)</f>
         <v>316800</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="6">
         <f>C14</f>
         <v>1000000</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="6">
         <f>B24</f>
         <v>316800</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="12">
         <f>C14-D26</f>
         <v>683200</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C27" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
+      <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="13" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="m7K9v/bn/0aaA+o+Z60WLbuF0EdFWGHolglUCk4THWsJoDB3hMAir1vnGrB5CrtAa8iZNUBHRu6/EQpvB1trFA==" saltValue="I4kotqym/Zk3lrG+MkTWVA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="m7aIuk7LZP5Ti6047V8BbYMwfkc86ojDytfg42MScVxBJbOXhcGE/OJ8G52PsiXaohaJrnXgvgFEcsJwWTzLeQ==" saltValue="nwpaFEbztg3leSGkiE8lEg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="B19 C20:C21">
     <cfRule type="expression" dxfId="0" priority="1">
